--- a/sample_data/stock_coil/Stock_coil_SAMPLE.xlsx
+++ b/sample_data/stock_coil/Stock_coil_SAMPLE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,16 +458,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SMP-COIL-DX54-1.5</t>
+          <t>SMP-COIL-DC04-1.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9912784407</t>
+          <t>9942868828</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8915</v>
+        <v>8157</v>
       </c>
     </row>
     <row r="3">
@@ -478,196 +478,196 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SMP-COIL-DC06-1.2</t>
+          <t>SMP-COIL-DC04-1.5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9979654147</t>
+          <t>9921668732</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11745</v>
+        <v>14174</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RA-04</t>
+          <t>RA-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SMP-COIL-DX54-1.2</t>
+          <t>SMP-COIL-DC04-0.7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9995199362</t>
+          <t>9939345092</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12556</v>
+        <v>8311</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RA-06</t>
+          <t>RA-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SMP-COIL-CR420-1.0</t>
+          <t>SMP-COIL-DC04-1.5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>9953091709</t>
+          <t>9936687537</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6213</v>
+        <v>13428</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RB-01</t>
+          <t>RA-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SMP-COIL-CR420-1.0</t>
+          <t>SMP-COIL-CR420-1.5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>9998930456</t>
+          <t>9947338124</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11061</v>
+        <v>4606</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RB-03</t>
+          <t>RA-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SMP-COIL-CR420-0.7</t>
+          <t>SMP-COIL-CR420-1.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9952213778</t>
+          <t>9947295260</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8635</v>
+        <v>7047</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RB-04</t>
+          <t>RB-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SMP-COIL-CR420-1.5</t>
+          <t>SMP-COIL-HX340-0.7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9910154493</t>
+          <t>9922448136</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13389</v>
+        <v>10724</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RB-05</t>
+          <t>RB-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SMP-COIL-DC04-0.8</t>
+          <t>SMP-COIL-HX340-1.5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9979583757</t>
+          <t>9945503389</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10427</v>
+        <v>5211</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RB-06</t>
+          <t>RB-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SMP-COIL-CR420-1.2</t>
+          <t>SMP-COIL-CR420-0.7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9916927215</t>
+          <t>9984093639</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7835</v>
+        <v>9303</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RB-07</t>
+          <t>RB-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SMP-COIL-DC06-1.0</t>
+          <t>SMP-COIL-HX340-1.5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9968802946</t>
+          <t>9935808537</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12441</v>
+        <v>5639</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RC-01</t>
+          <t>RB-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SMP-COIL-DX54-0.8</t>
+          <t>SMP-COIL-DC06-1.0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9931257157</t>
+          <t>9920709497</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9591</v>
+        <v>8314</v>
       </c>
     </row>
     <row r="13">
@@ -678,62 +678,62 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SMP-COIL-DX54-1.2</t>
+          <t>SMP-COIL-CR420-1.0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9922510327</t>
+          <t>9931831063</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8181</v>
+        <v>10565</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RC-05</t>
+          <t>RC-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SMP-COIL-DC04-0.8</t>
+          <t>SMP-COIL-HX340-0.7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>9976890827</t>
+          <t>9991756179</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9281</v>
+        <v>7303</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RC-06</t>
+          <t>RC-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SMP-COIL-HX340-1.2</t>
+          <t>SMP-COIL-DC06-0.8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9974759996</t>
+          <t>9972043515</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12236</v>
+        <v>10716</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RC-07</t>
+          <t>RC-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -743,37 +743,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9961484043</t>
+          <t>9953524491</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7622</v>
+        <v>5416</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RD-02</t>
+          <t>RC-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SMP-COIL-DC06-0.7</t>
+          <t>SMP-COIL-DC04-1.0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>9947077298</t>
+          <t>9963843426</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11298</v>
+        <v>8886</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RD-03</t>
+          <t>RC-07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -783,17 +783,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>9910344303</t>
+          <t>9938538251</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>9134</v>
+        <v>12679</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>RD-06</t>
+          <t>RD-01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -803,57 +803,57 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>9969934576</t>
+          <t>9945551614</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13324</v>
+        <v>6787</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RD-07</t>
+          <t>RD-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SMP-COIL-HX340-1.5</t>
+          <t>SMP-COIL-DX54-1.5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>9982937948</t>
+          <t>9945264581</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10680</v>
+        <v>14077</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RE-01</t>
+          <t>RD-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SMP-COIL-HX340-0.8</t>
+          <t>SMP-COIL-DX54-1.2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>9942051937</t>
+          <t>9958586340</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13868</v>
+        <v>8093</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RE-02</t>
+          <t>RD-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -863,17 +863,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9952704903</t>
+          <t>9916323852</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12249</v>
+        <v>6296</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RE-05</t>
+          <t>RD-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -883,237 +883,237 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9914968688</t>
+          <t>9990048665</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6568</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RE-06</t>
+          <t>RD-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SMP-COIL-DX54-1.0</t>
+          <t>SMP-COIL-DX54-1.2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>9923470708</t>
+          <t>9981016525</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11713</v>
+        <v>8619</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RE-07</t>
+          <t>RE-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SMP-COIL-CR420-0.7</t>
+          <t>SMP-COIL-DC04-1.5</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9929348212</t>
+          <t>9945812670</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11217</v>
+        <v>10073</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RF-03</t>
+          <t>RE-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SMP-COIL-HX340-1.0</t>
+          <t>SMP-COIL-CR420-0.8</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9993652460</t>
+          <t>9970897765</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11012</v>
+        <v>4553</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RF-04</t>
+          <t>RE-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SMP-COIL-HX340-1.5</t>
+          <t>SMP-COIL-DX54-0.8</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>9961003997</t>
+          <t>9978139880</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>9688</v>
+        <v>6243</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RF-05</t>
+          <t>RF-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SMP-COIL-CR420-1.5</t>
+          <t>SMP-COIL-DX54-1.5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9914818295</t>
+          <t>9936697396</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5621</v>
+        <v>7004</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RF-06</t>
+          <t>RF-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SMP-COIL-HX340-0.8</t>
+          <t>SMP-COIL-DC06-1.5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>9922130508</t>
+          <t>9981182864</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11610</v>
+        <v>4509</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RG-02</t>
+          <t>RF-04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SMP-COIL-DC06-1.0</t>
+          <t>SMP-COIL-CR420-0.7</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>9913885234</t>
+          <t>9925014631</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5253</v>
+        <v>10447</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RG-03</t>
+          <t>RF-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SMP-COIL-DC04-1.0</t>
+          <t>SMP-COIL-DC04-0.8</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>9958112135</t>
+          <t>9986149359</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10641</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RG-04</t>
+          <t>RF-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SMP-COIL-DC06-1.5</t>
+          <t>SMP-COIL-CR420-0.7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>9965304649</t>
+          <t>9981498611</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13772</v>
+        <v>6560</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RG-06</t>
+          <t>RG-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SMP-COIL-DC06-0.7</t>
+          <t>SMP-COIL-CR420-1.5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>9991804602</t>
+          <t>9932162965</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10767</v>
+        <v>8842</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RG-07</t>
+          <t>RG-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SMP-COIL-DC06-1.2</t>
+          <t>SMP-COIL-DX54-1.2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>9988270025</t>
+          <t>9938427073</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6844</v>
+        <v>13335</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RH-01</t>
+          <t>RG-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1123,91 +1123,151 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>9944269370</t>
+          <t>9979467853</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4653</v>
+        <v>11897</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RH-03</t>
+          <t>RG-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SMP-COIL-HX340-1.5</t>
+          <t>SMP-COIL-DC06-0.7</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>9931203129</t>
+          <t>9955377076</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5710</v>
+        <v>4844</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RH-04</t>
+          <t>RH-01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SMP-COIL-HX340-1.5</t>
+          <t>SMP-COIL-DC06-1.5</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>9950151803</t>
+          <t>9939557077</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11451</v>
+        <v>4617</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RH-06</t>
+          <t>RH-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SMP-COIL-HX340-0.8</t>
+          <t>SMP-COIL-DC04-0.8</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>9961632653</t>
+          <t>9919046318</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12416</v>
+        <v>5014</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>RH-04</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SMP-COIL-DC06-1.0</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>9999788677</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12453</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>RH-05</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SMP-COIL-DC06-1.5</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>9987337818</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12244</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>RH-06</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SMP-COIL-CR420-1.2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>9935556386</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>6045</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>RH-07</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>SMP-COIL-CR420-1.5</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>9958178682</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>13917</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SMP-COIL-CR420-1.0</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>9966851760</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11235</v>
       </c>
     </row>
   </sheetData>
